--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK71"/>
+  <dimension ref="A1:AK70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
         <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,16 +3927,16 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA43" t="n">
         <v>2.2</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,135 +9520,6 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.83333333334</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>45929</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,16 +3927,16 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.82</v>
+        <v>5.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4.05</v>
+        <v>1.57</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK70"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="11">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>1.57</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="47">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="61">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="63">
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,135 +9391,6 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.83333333334</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>45929</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK70" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4068,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.08</v>
+        <v>5.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AK71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.1</v>
+        <v>2.08</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.57</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.15</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.62</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="55">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N59" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="64">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,126 +9271,384 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3" t="n">
+        <v>45929.8125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3" t="n">
+        <v>45929.83333333334</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="3" t="n">
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK71"/>
+  <dimension ref="A1:AK73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45929.41666666666</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,16 +3927,16 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.97</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M37" t="n">
-        <v>4.7</v>
+        <v>3.59</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>3.56</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>1.65</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="55">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="62">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="71">
@@ -9529,126 +9529,384 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>45929.83333333334</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>45929.875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" s="3" t="n">
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>3.06</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,55 +4797,55 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>6.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.91</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="N37" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="M39" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N67" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>3.71</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
         <v>2.15</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,55 +5055,55 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="N39" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>1.77</v>
+        <v>2.91</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M65" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2607,10 +2607,10 @@
         <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.63</v>
       </c>
       <c r="N27" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.85</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="N28" t="n">
-        <v>1.77</v>
+        <v>3.56</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="M31" t="n">
-        <v>3.61</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.71</v>
+        <v>4.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,55 +5442,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.97</v>
       </c>
       <c r="N41" t="n">
-        <v>2.91</v>
+        <v>4.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.02</v>
+        <v>4.3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>1.65</v>
+        <v>2.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="47">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.96</v>
+        <v>7.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="N61" t="n">
-        <v>2.47</v>
+        <v>1.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="63">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,16 +8835,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.77083333334</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.875</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,264 +9649,6 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45929.83333333334</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>45929</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" s="3" t="n">
-        <v>45929.875</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>45929</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,49 +3636,49 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.2</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.71</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>6.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.59</v>
+        <v>4.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.56</v>
+        <v>1.38</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.63</v>
       </c>
       <c r="N35" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.85</v>
+        <v>1.78</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="N36" t="n">
-        <v>1.77</v>
+        <v>3.56</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>6.7</v>
+        <v>3.85</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK71"/>
+  <dimension ref="A1:AK73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.06</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.41</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,22 +3798,22 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.71</v>
+        <v>3.41</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,11 +3933,11 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>6.7</v>
+        <v>3.85</v>
       </c>
       <c r="M28" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.56</v>
+        <v>6.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.97</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>1.38</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>3.71</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N40" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="M43" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6000,7 +6000,7 @@
         <v>2.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.3</v>
+        <v>3.02</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="63">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="M65" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,16 +8835,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.77083333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="71">
@@ -9529,126 +9529,384 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>45929.83333333334</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>45929.875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" s="3" t="n">
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,49 +3894,49 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.2</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.77</v>
+        <v>3.41</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="N34" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.91</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3.05</v>
+        <v>3.61</v>
       </c>
       <c r="N38" t="n">
-        <v>4.05</v>
+        <v>3.71</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,55 +5571,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.02</v>
+        <v>2.08</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.01</v>
+        <v>3.35</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.99</v>
+        <v>3.02</v>
       </c>
       <c r="M45" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>2.01</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N46" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="55">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M62" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="64">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.77083333334</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,126 +9787,255 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3" t="n">
+        <v>45929.875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" s="3" t="n">
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>3.06</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>3.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.71</v>
+        <v>1.77</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.98</v>
+        <v>6.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4.05</v>
+        <v>1.38</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.7</v>
+        <v>1.56</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>3.97</v>
       </c>
       <c r="N40" t="n">
-        <v>1.38</v>
+        <v>4.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.97</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.85</v>
+        <v>1.78</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="N43" t="n">
-        <v>1.77</v>
+        <v>3.56</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="N44" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N62" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M63" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.6</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>3.06</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.61</v>
       </c>
       <c r="N35" t="n">
-        <v>1.53</v>
+        <v>3.71</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="M37" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.85</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>3.97</v>
       </c>
       <c r="N38" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>6.7</v>
+        <v>3.85</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="M40" t="n">
-        <v>3.97</v>
+        <v>3.59</v>
       </c>
       <c r="N40" t="n">
-        <v>4.4</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.78</v>
+        <v>6.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.59</v>
+        <v>4.8</v>
       </c>
       <c r="N43" t="n">
-        <v>3.56</v>
+        <v>1.38</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="M44" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>2.91</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M62" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N63" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="N30" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="N33" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.71</v>
+        <v>1.53</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>3.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="M42" t="n">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="M57" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>2.77</v>
+        <v>4.3</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M59" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
         <v>1.85</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK74"/>
+  <dimension ref="A1:AK78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>1.54</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45929.5</v>
+        <v>45929.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.76</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45929.52083333334</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.5</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45929.54166666666</v>
+        <v>45929.52083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="N28" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.17</v>
+        <v>1.81</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45929.5625</v>
+        <v>45929.54166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45929.58333333334</v>
+        <v>45929.5625</v>
       </c>
     </row>
     <row r="31">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
         <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.85</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>3.63</v>
       </c>
       <c r="N38" t="n">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.01</v>
+        <v>3.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="M46" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="N46" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,11 +6384,11 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z46" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z46" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.3</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="N47" t="n">
-        <v>1.65</v>
+        <v>3.56</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="51">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="M55" t="n">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="N55" t="n">
-        <v>3.27</v>
+        <v>2.53</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="58">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="M58" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="N58" t="n">
-        <v>2.77</v>
+        <v>4.3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N61" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.96</v>
+        <v>2.03</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z62" t="n">
         <v>1.65</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.19</v>
+        <v>2.03</v>
       </c>
       <c r="M63" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,10 +8700,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>2.13</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.1</v>
+        <v>2.96</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>1.45</v>
+        <v>2.47</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="67">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,27 +9271,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45929.77083333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,27 +9400,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="M72" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>5.4</v>
+        <v>2.09</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,126 +9916,642 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>45929.79166666666</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>45929.83333333334</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>45929.875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>45929.89583333334</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" s="3" t="n">
+      <c r="L78" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK78"/>
+  <dimension ref="A1:AK79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.06</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.27</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>1.88</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.76</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.63</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>1.77</v>
+        <v>2.91</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M38" t="n">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.05</v>
+        <v>6.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="N44" t="n">
-        <v>2.91</v>
+        <v>1.38</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.71</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="N47" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45929.59027777778</v>
+        <v>45929.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.99</v>
+        <v>3.02</v>
       </c>
       <c r="M49" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>2.01</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45929.59375</v>
+        <v>45929.59027777778</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N50" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45929.60416666666</v>
+        <v>45929.59375</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M58" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N58" t="n">
-        <v>4.3</v>
+        <v>2.53</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="59">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M61" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N63" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,16 +8700,16 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,16 +8829,16 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="66">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N66" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.23</v>
+        <v>2.96</v>
       </c>
       <c r="M67" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="N67" t="n">
-        <v>9.199999999999999</v>
+        <v>2.47</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="68">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M69" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="N69" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9529,27 +9529,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.23</v>
+        <v>7.1</v>
       </c>
       <c r="M71" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="N71" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,16 +9609,16 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="72">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="N72" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="O72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.16</v>
+        <v>2.85</v>
       </c>
       <c r="M73" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>2.09</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45929.77083333334</v>
+        <v>45929.67708333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="N74" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45929.79166666666</v>
+        <v>45929.77083333334</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M76" t="n">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="N76" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N77" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45929.89583333334</v>
+        <v>45929.875</v>
       </c>
     </row>
     <row r="78">
@@ -10447,111 +10447,240 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>45929.89583333334</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L78" t="n">
+      <c r="L79" t="n">
         <v>2.49</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M79" t="n">
         <v>3.25</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N79" t="n">
         <v>2.7</v>
       </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="3" t="n">
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>3.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.6</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N18" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.06</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.27</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>3.63</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M35" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N37" t="n">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>3.61</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>3.71</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="N46" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.75</v>
+        <v>6.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="N47" t="n">
-        <v>3.71</v>
+        <v>1.38</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>2.77</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.43</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8571,16 +8571,16 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="M64" t="n">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>3.27</v>
+        <v>4.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,16 +8829,16 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="M72" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="M73" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="O73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.06</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.76</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.21</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.08</v>
+        <v>6.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>3.7</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="M37" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>3.61</v>
+        <v>3.97</v>
       </c>
       <c r="N45" t="n">
-        <v>3.71</v>
+        <v>4.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="M46" t="n">
-        <v>3.97</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.7</v>
+        <v>1.65</v>
       </c>
       <c r="M47" t="n">
-        <v>4.8</v>
+        <v>3.63</v>
       </c>
       <c r="N47" t="n">
-        <v>1.38</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="M48" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA51" t="n">
         <v>2.1</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.23</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>5.2</v>
       </c>
       <c r="N59" t="n">
-        <v>2.77</v>
+        <v>5.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="M61" t="n">
-        <v>3.51</v>
+        <v>3.23</v>
       </c>
       <c r="N61" t="n">
-        <v>3.27</v>
+        <v>2.77</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N63" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8571,16 +8571,16 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.43</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,16 +8829,16 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M66" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M67" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N67" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA69" t="n">
         <v>1.85</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA74" t="n">
         <v>1.63</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.32</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.47</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3.36</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>6.8</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>3.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>1.97</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.76</v>
+        <v>1.99</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.06</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>3.06</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.3</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3129,34 +3129,34 @@
         <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y21" t="n">
         <v>2.3</v>
@@ -3165,16 +3165,16 @@
         <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3903,34 +3903,34 @@
         <v>3.32</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y27" t="n">
         <v>1.81</v>
@@ -3939,16 +3939,16 @@
         <v>1.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4161,28 +4161,28 @@
         <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
         <v>1.6</v>
@@ -4191,22 +4191,22 @@
         <v>2.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4290,34 +4290,34 @@
         <v>3.41</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y30" t="n">
         <v>2.17</v>
@@ -4326,16 +4326,16 @@
         <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.5</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.61</v>
+        <v>3.49</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4935,40 +4935,40 @@
         <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA35" t="n">
         <v>2.1</v>
@@ -4977,10 +4977,10 @@
         <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="N42" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5967,34 +5967,34 @@
         <v>2.91</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y43" t="n">
         <v>1.67</v>
@@ -6003,16 +6003,16 @@
         <v>2.07</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6225,34 +6225,34 @@
         <v>4.4</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="Y45" t="n">
         <v>1.5</v>
@@ -6267,10 +6267,10 @@
         <v>1.82</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6870,34 +6870,34 @@
         <v>3.2</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Y50" t="n">
         <v>2.15</v>
@@ -6906,16 +6906,16 @@
         <v>1.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6999,34 +6999,34 @@
         <v>1.65</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y51" t="n">
         <v>1.55</v>
@@ -7041,10 +7041,10 @@
         <v>1.65</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.54</v>
+        <v>1.09</v>
       </c>
       <c r="M52" t="n">
-        <v>3.03</v>
+        <v>7.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.53</v>
+        <v>13.1</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>3.36</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="M61" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="M63" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N63" t="n">
-        <v>4.3</v>
+        <v>2.77</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,16 +8829,16 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,16 +9222,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="M71" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="N72" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O72" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T72" t="n">
         <v>2.09</v>
       </c>
-      <c r="O72" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P72" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S72" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U72" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V72" t="n">
         <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X72" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="Y72" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC72" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z72" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AD72" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="N73" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.01</v>
+        <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>4.54</v>
       </c>
       <c r="O3" t="n">
-        <v>3.88</v>
+        <v>2.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.97</v>
+        <v>4.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
         <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.61</v>
+        <v>4.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>3.01</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.54</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.39</v>
+        <v>3.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.9</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
         <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
         <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.15</v>
+        <v>4.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.87</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>3.47</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>5.55</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.75</v>
+        <v>1.94</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>6.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>2.71</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.41</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>6.49</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.52</v>
+        <v>4.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.36</v>
+        <v>4.32</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>5.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>4.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>4.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.43</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>3.27</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.52</v>
+        <v>2.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>7.65</v>
+        <v>1.92</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>7.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.99</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>1.28</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>7.65</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.74</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.82</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.06</v>
+        <v>3.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.21</v>
+        <v>3.32</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>2.67</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.82</v>
+        <v>4.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>3.84</v>
       </c>
       <c r="N27" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.02</v>
+        <v>3.31</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>3.44</v>
+        <v>6.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.98</v>
+        <v>2.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.84</v>
+        <v>2.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
-        <v>2.07</v>
+        <v>3.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.12</v>
       </c>
-      <c r="X28" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.38</v>
+        <v>2.19</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.98</v>
+        <v>1.68</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.55</v>
       </c>
-      <c r="M29" t="n">
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.2</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.36</v>
       </c>
-      <c r="X30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X32" t="n">
         <v>3.6</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4671,58 +4671,58 @@
         <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.95</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.49</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>4.55</v>
       </c>
       <c r="O34" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.52</v>
+        <v>5.05</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="T34" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>5.95</v>
+        <v>2.98</v>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.8</v>
+        <v>3.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="T35" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.68</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>3.71</v>
       </c>
       <c r="O36" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V36" t="n">
         <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q38" t="n">
         <v>4.5</v>
       </c>
-      <c r="M38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.85</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>3.97</v>
       </c>
       <c r="N39" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
-        <v>3.7</v>
+        <v>2.13</v>
       </c>
       <c r="P39" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.67</v>
+        <v>4.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="U39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.5</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.19</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="T40" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="M41" t="n">
-        <v>2.9</v>
+        <v>3.49</v>
       </c>
       <c r="N41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O41" t="n">
         <v>3.8</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.33</v>
+        <v>2.52</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.65</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC42" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q43" t="n">
         <v>2.91</v>
       </c>
-      <c r="O43" t="n">
+      <c r="R43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S43" t="n">
         <v>2.98</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.31</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC43" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="M45" t="n">
-        <v>3.97</v>
+        <v>4.6</v>
       </c>
       <c r="N45" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="P45" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.72</v>
+        <v>6.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>4.99</v>
+        <v>4.15</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>4.5</v>
       </c>
       <c r="M46" t="n">
         <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>5.18</v>
       </c>
       <c r="P46" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>4.83</v>
+        <v>5.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>2.54</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O48" t="n">
         <v>3.7</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.85</v>
-      </c>
       <c r="P48" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.82</v>
+        <v>2.67</v>
       </c>
       <c r="R48" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="T48" t="n">
-        <v>3.74</v>
+        <v>2.48</v>
       </c>
       <c r="U48" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="X48" t="n">
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6741,34 +6741,34 @@
         <v>2.01</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y49" t="n">
         <v>1.79</v>
@@ -6777,16 +6777,16 @@
         <v>1.91</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="M52" t="n">
-        <v>7.3</v>
+        <v>4.25</v>
       </c>
       <c r="N52" t="n">
-        <v>13.1</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="P52" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="Q52" t="n">
-        <v>8.9</v>
+        <v>4.61</v>
       </c>
       <c r="R52" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S52" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="T52" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="U52" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X52" t="n">
-        <v>7.3</v>
+        <v>5.45</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.36</v>
+        <v>2.63</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH52" t="n">
-        <v>4.85</v>
+        <v>2.26</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.63</v>
+        <v>2.54</v>
       </c>
       <c r="M54" t="n">
-        <v>4.25</v>
+        <v>3.03</v>
       </c>
       <c r="N54" t="n">
-        <v>4.5</v>
+        <v>2.53</v>
       </c>
       <c r="O54" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.61</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="T54" t="n">
-        <v>1.98</v>
+        <v>3.04</v>
       </c>
       <c r="U54" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="X54" t="n">
-        <v>5.45</v>
+        <v>2.88</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>3.74</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="M55" t="n">
-        <v>3.64</v>
+        <v>4.6</v>
       </c>
       <c r="N55" t="n">
-        <v>2.4</v>
+        <v>4.56</v>
       </c>
       <c r="O55" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="P55" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.9</v>
+        <v>4.55</v>
       </c>
       <c r="R55" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S55" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T55" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="U55" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X55" t="n">
-        <v>4.2</v>
+        <v>6.15</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.37</v>
+        <v>2.69</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.47</v>
+        <v>2.32</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,62 +7635,62 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="M56" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="N56" t="n">
-        <v>4.56</v>
+        <v>13.1</v>
       </c>
       <c r="O56" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X56" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD56" t="n">
         <v>2.02</v>
       </c>
-      <c r="P56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X56" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.32</v>
+        <v>4.85</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,62 +8022,62 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y59" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD59" t="n">
         <v>1.72</v>
       </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M60" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N61" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="M63" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8676,34 +8676,34 @@
         <v>5.2</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y64" t="n">
         <v>1.9</v>
@@ -8712,16 +8712,16 @@
         <v>1.8</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.23</v>
+        <v>7.1</v>
       </c>
       <c r="M68" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="N68" t="n">
-        <v>9.199999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,16 +9222,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z68" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9699,16 +9699,16 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="M72" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O72" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="P72" t="n">
         <v>2.44</v>
@@ -9723,10 +9723,10 @@
         <v>4.1</v>
       </c>
       <c r="T72" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="U72" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V72" t="n">
         <v>1.01</v>
@@ -9744,10 +9744,10 @@
         <v>2.65</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC72" t="n">
         <v>1.38</v>
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="M73" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="N73" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="O73" t="n">
         <v>3.5</v>
@@ -9843,7 +9843,7 @@
         <v>2.45</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R73" t="n">
         <v>1.19</v>
@@ -9861,19 +9861,19 @@
         <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X73" t="n">
         <v>5.55</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z73" t="n">
         <v>2.63</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB73" t="n">
         <v>1.73</v>
@@ -9966,34 +9966,34 @@
         <v>11</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y74" t="n">
         <v>1.28</v>
@@ -10008,10 +10008,10 @@
         <v>2.15</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.59</v>
+        <v>3.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N79" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.54</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="P3" t="n">
         <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
         <v>3.3</v>
@@ -831,10 +831,10 @@
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
         <v>2.34</v>
@@ -868,7 +868,7 @@
         <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="P4" t="n">
         <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
@@ -963,19 +963,19 @@
         <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
         <v>4.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
         <v>2.07</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.47</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.82</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.41</v>
       </c>
-      <c r="AA9" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.19</v>
+        <v>1.51</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>2.36</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>3.36</v>
+        <v>4.32</v>
       </c>
       <c r="N10" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>5.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>1.54</v>
+        <v>6.8</v>
       </c>
       <c r="O12" t="n">
-        <v>6.49</v>
+        <v>1.97</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.31</v>
+        <v>6.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="X12" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.63</v>
+        <v>3.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>2.71</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.41</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.55</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.74</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y16" t="n">
         <v>2.25</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>4.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
         <v>1.28</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.92</v>
+        <v>7.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.2</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.88</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.21</v>
       </c>
       <c r="N18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.28</v>
       </c>
-      <c r="O18" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.06</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.43</v>
+        <v>3.06</v>
       </c>
       <c r="M20" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
         <v>2.57</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>3.84</v>
       </c>
       <c r="N26" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.02</v>
+        <v>3.31</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>3.44</v>
+        <v>6.33</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>2.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.84</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="T27" t="n">
-        <v>2.07</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.12</v>
       </c>
-      <c r="X27" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1.38</v>
+        <v>2.19</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O28" t="n">
-        <v>2.92</v>
+        <v>3.48</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.05</v>
+        <v>2.82</v>
       </c>
       <c r="R28" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
         <v>3.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.54</v>
-      </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4206,7 +4206,7 @@
         <v>1.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
         <v>3.04</v>
@@ -4320,22 +4320,22 @@
         <v>2.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AB30" t="n">
         <v>1.14</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.46</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="O32" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T32" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.19</v>
       </c>
-      <c r="X32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="P33" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="T33" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
         <v>1.08</v>
       </c>
       <c r="W33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.57</v>
       </c>
-      <c r="X33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AA33" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.55</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.25</v>
+        <v>3.68</v>
       </c>
       <c r="P34" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.05</v>
+        <v>2.91</v>
       </c>
       <c r="R34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="O35" t="n">
-        <v>2.98</v>
+        <v>5.18</v>
       </c>
       <c r="P35" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA35" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.61</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3.71</v>
+        <v>2.96</v>
       </c>
       <c r="O36" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="U36" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
         <v>1.04</v>
       </c>
       <c r="W36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.22</v>
       </c>
-      <c r="X36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.7</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="N37" t="n">
-        <v>1.38</v>
+        <v>5.79</v>
       </c>
       <c r="O37" t="n">
-        <v>5.95</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S37" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AA37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O38" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="P38" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="T38" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>3.97</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="O39" t="n">
-        <v>2.13</v>
+        <v>7.8</v>
       </c>
       <c r="P39" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.72</v>
+        <v>1.7</v>
       </c>
       <c r="R39" t="n">
         <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T39" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.88</v>
+        <v>4.82</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S40" t="n">
-        <v>3.42</v>
+        <v>2.23</v>
       </c>
       <c r="T40" t="n">
-        <v>2.39</v>
+        <v>3.74</v>
       </c>
       <c r="U40" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="X40" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.95</v>
+        <v>1.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.49</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.05</v>
+        <v>4.55</v>
       </c>
       <c r="O41" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.52</v>
+        <v>5.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="R42" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S42" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="V42" t="n">
         <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>4.83</v>
+        <v>4.05</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD42" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.54</v>
+        <v>1.56</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.04</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,77 +6087,77 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>3.97</v>
       </c>
       <c r="N44" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="O44" t="n">
-        <v>7.8</v>
+        <v>2.13</v>
       </c>
       <c r="P44" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.7</v>
+        <v>4.72</v>
       </c>
       <c r="R44" t="n">
         <v>1.22</v>
       </c>
       <c r="S44" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH44" t="n">
         <v>2.25</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.02</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.44</v>
       </c>
-      <c r="M45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N45" t="n">
-        <v>7</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AC45" t="n">
         <v>1.5</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="O46" t="n">
-        <v>5.18</v>
+        <v>5.95</v>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="T46" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U46" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="M48" t="n">
-        <v>3.85</v>
+        <v>3.49</v>
       </c>
       <c r="N48" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P48" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S48" t="n">
         <v>3.3</v>
       </c>
       <c r="T48" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="U48" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AD48" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S50" t="n">
         <v>2.74</v>
@@ -6888,7 +6888,7 @@
         <v>2.94</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
@@ -6915,7 +6915,7 @@
         <v>1.85</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,77 +7119,77 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y52" t="n">
         <v>1.63</v>
       </c>
-      <c r="M52" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X52" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z52" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AC52" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.26</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="M53" t="n">
-        <v>3.68</v>
+        <v>3.03</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="O53" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="T53" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="U53" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X53" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.55</v>
+        <v>3.74</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="M54" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P54" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="Q54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S54" t="n">
         <v>3.3</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.44</v>
       </c>
-      <c r="S54" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC54" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="M56" t="n">
-        <v>7.3</v>
+        <v>4.25</v>
       </c>
       <c r="N56" t="n">
-        <v>13.1</v>
+        <v>4.56</v>
       </c>
       <c r="O56" t="n">
-        <v>1.51</v>
+        <v>2.03</v>
       </c>
       <c r="P56" t="n">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="Q56" t="n">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S56" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="T56" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="U56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X56" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA56" t="n">
         <v>1.89</v>
       </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X56" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB56" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.02</v>
+        <v>2.73</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH56" t="n">
-        <v>4.85</v>
+        <v>2.3</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,77 +7764,77 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X57" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z57" t="n">
         <v>2.63</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T57" t="n">
+      <c r="AA57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH57" t="n">
         <v>2.28</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.47</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="N59" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="O59" t="n">
-        <v>3.46</v>
+        <v>1.89</v>
       </c>
       <c r="P59" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y59" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q59" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="Z59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA59" t="n">
         <v>3.42</v>
       </c>
-      <c r="U59" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AB59" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O60" t="n">
-        <v>2.53</v>
+        <v>3.46</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S60" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="U60" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V60" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W60" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X60" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="M61" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M62" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y62" t="n">
         <v>1.85</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N63" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O63" t="n">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="P63" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.99</v>
+        <v>6.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S63" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="T63" t="n">
-        <v>2.51</v>
+        <v>3.04</v>
       </c>
       <c r="U63" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V63" t="n">
         <v>1.01</v>
       </c>
       <c r="W63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.19</v>
       </c>
-      <c r="X63" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC63" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.43</v>
+        <v>2.09</v>
       </c>
       <c r="M64" t="n">
-        <v>5.2</v>
+        <v>3.51</v>
       </c>
       <c r="N64" t="n">
-        <v>5.2</v>
+        <v>3.27</v>
       </c>
       <c r="O64" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="P64" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>9.550000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="R64" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S64" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="T64" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="U64" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V64" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
         <v>1.3</v>
       </c>
       <c r="X64" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH64" t="n">
-        <v>2.95</v>
+        <v>1.68</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N65" t="n">
-        <v>4.3</v>
+        <v>2.77</v>
       </c>
       <c r="O65" t="n">
-        <v>2.14</v>
+        <v>2.79</v>
       </c>
       <c r="P65" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>6.1</v>
+        <v>3.57</v>
       </c>
       <c r="R65" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S65" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T65" t="n">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="U65" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="V65" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W65" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="X65" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="Y65" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.74</v>
+        <v>2.71</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N66" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M67" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N67" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N69" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="P69" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q69" t="n">
-        <v>7.48</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S69" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="T69" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="U69" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W69" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="X69" t="n">
-        <v>6.55</v>
+        <v>3.34</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="Z69" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AH69" t="n">
-        <v>3.6</v>
+        <v>2.04</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>7.64</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,77 +9570,77 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M71" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X71" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH71" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="M76" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="N76" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y76" t="n">
         <v>2.4</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M77" t="n">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="N77" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,61 +10473,61 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="M78" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S78" t="n">
         <v>3.1</v>
       </c>
-      <c r="N78" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45929.89583333334</v>
+        <v>45929.875</v>
       </c>
     </row>
     <row r="79">

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.58</v>
+        <v>3.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.96</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.55</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AA3" t="n">
-        <v>4.15</v>
+        <v>4.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.68</v>
+        <v>2.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>4.96</v>
       </c>
       <c r="R4" t="n">
         <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.61</v>
+        <v>4.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.82</v>
+        <v>6.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.52</v>
+        <v>3.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>2.71</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45929.45833333334</v>
+        <v>45929.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.41</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="N11" t="n">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.8</v>
+        <v>5.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.47</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.82</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.5</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.41</v>
       </c>
-      <c r="AA13" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.19</v>
+        <v>1.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.59</v>
+        <v>2.36</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>4.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>2.51</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.24</v>
+        <v>4.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>7.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>2.56</v>
+        <v>7.65</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.96</v>
+        <v>1.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>2.62</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>7.65</v>
+        <v>3.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>1.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.2</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.65</v>
-      </c>
       <c r="Q26" t="n">
-        <v>3.31</v>
+        <v>3.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>6.33</v>
+        <v>3.44</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.81</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.8</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O27" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.31</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>2.07</v>
       </c>
       <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X27" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.24</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.82</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.35</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.36</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.55</v>
       </c>
-      <c r="M30" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.57</v>
+        <v>2.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="N32" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.27</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.49</v>
-      </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.08</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.37</v>
-      </c>
       <c r="X33" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.97</v>
+        <v>1.51</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.9</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="T34" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X34" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q35" t="n">
         <v>4.5</v>
       </c>
-      <c r="M35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O35" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.09</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="S35" t="n">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="T35" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="X35" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.4</v>
       </c>
-      <c r="M36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="AA36" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.92</v>
-      </c>
       <c r="AB36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>5.79</v>
+        <v>1.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T37" t="n">
         <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.62</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.46</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="O38" t="n">
-        <v>2.54</v>
+        <v>3.7</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>2.67</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="U38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.42</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.83</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="O39" t="n">
-        <v>7.8</v>
+        <v>2.86</v>
       </c>
       <c r="P39" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="R39" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S39" t="n">
         <v>3.42</v>
       </c>
       <c r="T39" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U39" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X39" t="n">
-        <v>4.79</v>
+        <v>4.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="N41" t="n">
-        <v>4.55</v>
+        <v>5.79</v>
       </c>
       <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.25</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="X41" t="n">
-        <v>3.52</v>
+        <v>4.83</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AD41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH41" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.85</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>3.61</v>
       </c>
       <c r="N43" t="n">
-        <v>1.77</v>
+        <v>3.71</v>
       </c>
       <c r="O43" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="P43" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.67</v>
+        <v>4.35</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T43" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
-        <v>2.13</v>
+        <v>3.68</v>
       </c>
       <c r="P44" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.72</v>
+        <v>2.91</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="T44" t="n">
-        <v>2.17</v>
+        <v>2.76</v>
       </c>
       <c r="U44" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X44" t="n">
-        <v>4.99</v>
+        <v>3.28</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.98</v>
+        <v>3.08</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="M45" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N45" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
-        <v>2.86</v>
+        <v>1.92</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="M46" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
-        <v>5.95</v>
+        <v>2.98</v>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.8</v>
+        <v>3.38</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="T46" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U46" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y46" t="n">
         <v>1.68</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X46" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Z46" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="M47" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>4.55</v>
       </c>
       <c r="O47" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="P47" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.25</v>
+        <v>5.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V47" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X47" t="n">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="M48" t="n">
-        <v>3.49</v>
+        <v>4.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="O48" t="n">
-        <v>3.8</v>
+        <v>5.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="T48" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U48" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="V48" t="n">
         <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.08</v>
+        <v>2.47</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,22 +7119,22 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P52" t="n">
         <v>2.3</v>
       </c>
-      <c r="O52" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.26</v>
-      </c>
       <c r="Q52" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="R52" t="n">
         <v>1.28</v>
@@ -7143,54 +7143,54 @@
         <v>3.3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U52" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.2</v>
       </c>
-      <c r="X52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AI52" t="n">
         <v>0</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45929.625</v>
+        <v>45929.60416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,62 +7248,62 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.54</v>
+        <v>1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>3.03</v>
+        <v>4.4</v>
       </c>
       <c r="N53" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X53" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD53" t="n">
         <v>2.53</v>
       </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="O54" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="T54" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="U54" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X54" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.44</v>
+        <v>3.74</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M56" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>4.56</v>
+        <v>2.3</v>
       </c>
       <c r="O56" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R56" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="T56" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="U56" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X56" t="n">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M57" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="N57" t="n">
         <v>4.56</v>
       </c>
       <c r="O57" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="P57" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S57" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="T57" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U57" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>5.45</v>
+        <v>6.15</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="M59" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="P59" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="Q59" t="n">
-        <v>9.550000000000001</v>
+        <v>3.22</v>
       </c>
       <c r="R59" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="S59" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.94</v>
+        <v>2.23</v>
       </c>
       <c r="U59" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V59" t="n">
         <v>1.02</v>
       </c>
       <c r="W59" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X59" t="n">
-        <v>2.97</v>
+        <v>4.6</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.42</v>
+        <v>2.44</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.48</v>
+        <v>1.51</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.95</v>
+        <v>1.57</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45929.64583333334</v>
+        <v>45929.625</v>
       </c>
     </row>
     <row r="60">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,77 +8151,77 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N60" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="O60" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="P60" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R60" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="T60" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="U60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X60" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
         <v>1.25</v>
       </c>
-      <c r="V60" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X60" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH60" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8289,52 +8289,52 @@
         <v>3.4</v>
       </c>
       <c r="O61" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>3.99</v>
       </c>
       <c r="R61" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="T61" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="U61" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="V61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="X61" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,77 +8409,77 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
-        <v>2.51</v>
+        <v>3.46</v>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S62" t="n">
-        <v>3.09</v>
+        <v>2.38</v>
       </c>
       <c r="T62" t="n">
-        <v>2.51</v>
+        <v>3.42</v>
       </c>
       <c r="U62" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="V62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W62" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="X62" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="AB62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH62" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.09</v>
+        <v>1.43</v>
       </c>
       <c r="M64" t="n">
-        <v>3.51</v>
+        <v>5.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.27</v>
+        <v>5.2</v>
       </c>
       <c r="O64" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="R64" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S64" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="T64" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U64" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W64" t="n">
         <v>1.3</v>
       </c>
       <c r="X64" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="M65" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="P65" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.57</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T65" t="n">
         <v>3.1</v>
       </c>
-      <c r="T65" t="n">
-        <v>2.54</v>
-      </c>
       <c r="U65" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V65" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W65" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="X65" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA65" t="n">
         <v>3.8</v>
       </c>
-      <c r="Y65" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.71</v>
-      </c>
       <c r="AB65" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,78 +8925,78 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.19</v>
+        <v>2.23</v>
       </c>
       <c r="M66" t="n">
-        <v>2.98</v>
+        <v>3.23</v>
       </c>
       <c r="N66" t="n">
-        <v>2.13</v>
+        <v>2.77</v>
       </c>
       <c r="O66" t="n">
-        <v>3.75</v>
+        <v>2.79</v>
       </c>
       <c r="P66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z66" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q66" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T66" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U66" t="n">
+      <c r="AA66" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
         <v>1.28</v>
       </c>
-      <c r="V66" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X66" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z66" t="n">
+      <c r="AH66" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA66" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI66" t="n">
         <v>0</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45929.65625</v>
+        <v>45929.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45929.66666666666</v>
+        <v>45929.65625</v>
       </c>
     </row>
     <row r="69">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,77 +9312,77 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M69" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X69" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH69" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N69" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O69" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P69" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>5</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X69" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>7.48</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9658,27 +9658,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M72" t="n">
         <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
-        <v>3.78</v>
+        <v>2.38</v>
       </c>
       <c r="P72" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S72" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T72" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="U72" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="V72" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W72" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="X72" t="n">
-        <v>5.4</v>
+        <v>3.34</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA72" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45929.67708333334</v>
+        <v>45929.66666666666</v>
       </c>
     </row>
     <row r="73">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M73" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="N73" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="O73" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P73" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R73" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S73" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="T73" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="U73" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V73" t="n">
         <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X73" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK79"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>2.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>4.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
         <v>1.71</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.96</v>
+        <v>3.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
         <v>1.04</v>
       </c>
       <c r="W4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.55</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1581,34 +1581,34 @@
         <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.95</v>
+        <v>7.59</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
         <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
         <v>2.25</v>
@@ -1617,16 +1617,16 @@
         <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.47</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="O10" t="n">
-        <v>4.82</v>
+        <v>6.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.39</v>
+        <v>4.63</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>3.47</v>
       </c>
       <c r="M11" t="n">
-        <v>4.32</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.32</v>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.96</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.51</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.15</v>
+        <v>2.24</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2862,28 +2862,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="P19" t="n">
         <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.2</v>
+        <v>7.55</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
         <v>2.98</v>
@@ -2901,7 +2901,7 @@
         <v>2.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Z19" t="n">
         <v>1.7</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.06</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
         <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3129,16 +3129,16 @@
         <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="P21" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
         <v>2.62</v>
@@ -3153,7 +3153,7 @@
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
         <v>2.84</v>
@@ -3168,13 +3168,13 @@
         <v>3.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
-        <v>3.32</v>
+        <v>2.21</v>
       </c>
       <c r="O26" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.96</v>
+        <v>2.82</v>
       </c>
       <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.2</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.65</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.31</v>
+        <v>3.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>6.33</v>
+        <v>3.44</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>1.81</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O28" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.05</v>
+        <v>3.31</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>3.5</v>
+        <v>2.07</v>
       </c>
       <c r="U28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X28" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.24</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4161,28 +4161,28 @@
         <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>4.01</v>
       </c>
       <c r="P29" t="n">
         <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="R29" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S29" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
         <v>1.6</v>
@@ -4194,19 +4194,19 @@
         <v>2.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4290,16 +4290,16 @@
         <v>3.41</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
         <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
         <v>2.55</v>
@@ -4308,7 +4308,7 @@
         <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
         <v>1.03</v>
@@ -4326,16 +4326,16 @@
         <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AB30" t="n">
         <v>1.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.49</v>
+        <v>3.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="O31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,58 +4539,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>6.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.46</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="O32" t="n">
-        <v>2.54</v>
+        <v>5.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.02</v>
+        <v>3.66</v>
       </c>
       <c r="T32" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
         <v>2.11</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N33" t="n">
-        <v>1.53</v>
+        <v>5.79</v>
       </c>
       <c r="O33" t="n">
-        <v>5.18</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>5.5</v>
+        <v>4.83</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AD33" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,58 +4797,58 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.96</v>
+        <v>1.2</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="P34" t="n">
-        <v>1.98</v>
+        <v>2.57</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="T34" t="n">
-        <v>3.32</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>2.7</v>
+        <v>4.79</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.24</v>
+        <v>1.47</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
         <v>1.82</v>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4935,13 +4935,13 @@
         <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="P35" t="n">
         <v>1.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R35" t="n">
         <v>1.47</v>
@@ -4956,13 +4956,13 @@
         <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
         <v>1.37</v>
       </c>
       <c r="X35" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="Y35" t="n">
         <v>2.25</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.13</v>
+        <v>3.68</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.72</v>
+        <v>2.91</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="T36" t="n">
-        <v>2.17</v>
+        <v>2.76</v>
       </c>
       <c r="U36" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>4.99</v>
+        <v>3.28</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>3.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>7.8</v>
+        <v>2.86</v>
       </c>
       <c r="P37" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
         <v>3.42</v>
       </c>
       <c r="T37" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>4.79</v>
+        <v>4.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.85</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.77</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
-        <v>3.7</v>
+        <v>1.92</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.67</v>
+        <v>6.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="U38" t="n">
         <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
         <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AB38" t="n">
         <v>1.42</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="N39" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O39" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>5.79</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AA41" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.71</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
-        <v>2.31</v>
+        <v>5.18</v>
       </c>
       <c r="P43" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.35</v>
+        <v>2.09</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
-        <v>3.68</v>
+        <v>2.87</v>
       </c>
       <c r="P44" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.91</v>
+        <v>4.76</v>
       </c>
       <c r="R44" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="S44" t="n">
-        <v>2.98</v>
+        <v>2.23</v>
       </c>
       <c r="T44" t="n">
-        <v>2.76</v>
+        <v>3.74</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W44" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="X44" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,62 +6216,62 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="M45" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.25</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T45" t="n">
         <v>3.2</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V45" t="n">
         <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="X45" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.56</v>
+        <v>4.18</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AC45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD45" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.4</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X46" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA46" t="n">
         <v>2.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="M47" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="N47" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="O47" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH47" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
-        <v>5.95</v>
+        <v>2.98</v>
       </c>
       <c r="P48" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="U48" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X48" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N51" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O51" t="n">
         <v>4.33</v>
@@ -7014,37 +7014,37 @@
         <v>3.22</v>
       </c>
       <c r="T51" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X51" t="n">
         <v>4.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH51" t="n">
         <v>1.22</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7119,34 +7119,34 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O52" t="n">
         <v>4.33</v>
       </c>
       <c r="P52" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R52" t="n">
         <v>1.28</v>
       </c>
       <c r="S52" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U52" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
@@ -7158,22 +7158,22 @@
         <v>4.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z52" t="n">
         <v>2.3</v>
       </c>
       <c r="AA52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD52" t="n">
         <v>2.35</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.33</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,77 +7248,77 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="M53" t="n">
-        <v>4.4</v>
+        <v>7.25</v>
       </c>
       <c r="N53" t="n">
-        <v>4.56</v>
+        <v>13.1</v>
       </c>
       <c r="O53" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="P53" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.61</v>
+        <v>8.9</v>
       </c>
       <c r="R53" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S53" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="T53" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="U53" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
       </c>
       <c r="W53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X53" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
         <v>1.08</v>
       </c>
-      <c r="X53" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH53" t="n">
-        <v>2.28</v>
+        <v>4.85</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,62 +7377,62 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.54</v>
+        <v>1.63</v>
       </c>
       <c r="M54" t="n">
-        <v>3.03</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X54" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD54" t="n">
         <v>2.53</v>
       </c>
-      <c r="O54" t="n">
-        <v>3</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.6</v>
+        <v>2.54</v>
       </c>
       <c r="M57" t="n">
-        <v>4.25</v>
+        <v>3.03</v>
       </c>
       <c r="N57" t="n">
-        <v>4.56</v>
+        <v>2.53</v>
       </c>
       <c r="O57" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>4.15</v>
+        <v>2.58</v>
       </c>
       <c r="T57" t="n">
-        <v>1.95</v>
+        <v>3.04</v>
       </c>
       <c r="U57" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W57" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="X57" t="n">
-        <v>6.15</v>
+        <v>2.88</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.31</v>
+        <v>2.15</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.93</v>
+        <v>1.7</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.89</v>
+        <v>3.74</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.73</v>
+        <v>1.9</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.17</v>
+        <v>2.35</v>
       </c>
       <c r="M58" t="n">
-        <v>7.25</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>13.1</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC58" t="n">
         <v>1.51</v>
       </c>
-      <c r="P58" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X58" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD58" t="n">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>4.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>4.56</v>
       </c>
       <c r="O59" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="P59" t="n">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="S59" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T59" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="U59" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="V59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X59" t="n">
-        <v>4.6</v>
+        <v>6.15</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.42</v>
+        <v>2.73</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>3.27</v>
+        <v>2.3</v>
       </c>
       <c r="O60" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="P60" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="R60" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S60" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="T60" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="U60" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="V60" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W60" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="X60" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,37 +8280,37 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="O61" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
       <c r="P61" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.99</v>
+        <v>3.57</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S61" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="T61" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U61" t="n">
         <v>1.46</v>
       </c>
       <c r="V61" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
         <v>1.19</v>
@@ -8319,22 +8319,22 @@
         <v>3.8</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
-        <v>3.46</v>
+        <v>2.86</v>
       </c>
       <c r="P62" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R62" t="n">
         <v>1.49</v>
       </c>
       <c r="S62" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="T62" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U62" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V62" t="n">
         <v>1.04</v>
       </c>
       <c r="W62" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X62" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="M63" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="O63" t="n">
-        <v>2.14</v>
+        <v>2.59</v>
       </c>
       <c r="P63" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.1</v>
+        <v>3.83</v>
       </c>
       <c r="R63" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S63" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="T63" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="U63" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="V63" t="n">
         <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="X63" t="n">
-        <v>2.92</v>
+        <v>3.74</v>
       </c>
       <c r="Y63" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH63" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="M64" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="O64" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="P64" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q64" t="n">
-        <v>9.550000000000001</v>
+        <v>5.99</v>
       </c>
       <c r="R64" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S64" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="U64" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V64" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X64" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH64" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M65" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X65" t="n">
         <v>3.4</v>
       </c>
-      <c r="N65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.85</v>
-      </c>
       <c r="Y65" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.23</v>
+        <v>1.43</v>
       </c>
       <c r="M66" t="n">
-        <v>3.23</v>
+        <v>5.2</v>
       </c>
       <c r="N66" t="n">
-        <v>2.77</v>
+        <v>5.2</v>
       </c>
       <c r="O66" t="n">
-        <v>2.79</v>
+        <v>1.88</v>
       </c>
       <c r="P66" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.57</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R66" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S66" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="T66" t="n">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="U66" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="V66" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W66" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="X66" t="n">
-        <v>3.8</v>
+        <v>3.11</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.71</v>
+        <v>3.28</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.22</v>
+        <v>1.51</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,58 +9054,58 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M67" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N67" t="n">
-        <v>2.47</v>
+        <v>2.13</v>
       </c>
       <c r="O67" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="R67" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S67" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T67" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U67" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V67" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W67" t="n">
         <v>1.42</v>
       </c>
       <c r="X67" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="AB67" t="n">
         <v>1.18</v>
       </c>
       <c r="AC67" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>1.8</v>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,58 +9183,58 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M68" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N68" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="O68" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="P68" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="R68" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T68" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U68" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V68" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W68" t="n">
         <v>1.42</v>
       </c>
       <c r="X68" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AB68" t="n">
         <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD68" t="n">
         <v>1.8</v>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7.48</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>7.64</v>
+        <v>1.23</v>
       </c>
       <c r="M70" t="n">
-        <v>4.69</v>
+        <v>5.1</v>
       </c>
       <c r="N70" t="n">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O70" t="n">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="P70" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.89</v>
+        <v>7.48</v>
       </c>
       <c r="R70" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S70" t="n">
-        <v>2.98</v>
+        <v>3.98</v>
       </c>
       <c r="T70" t="n">
-        <v>2.51</v>
+        <v>1.93</v>
       </c>
       <c r="U70" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="V70" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X70" t="n">
-        <v>3.95</v>
+        <v>6.55</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC70" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.08</v>
+        <v>3.6</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="M72" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O72" t="n">
+        <v>7</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X72" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y72" t="n">
         <v>1.8</v>
       </c>
-      <c r="M72" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N72" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P72" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>5</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U72" t="n">
+      <c r="Z72" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB72" t="n">
         <v>1.38</v>
       </c>
-      <c r="V72" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X72" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC72" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH72" t="n">
-        <v>2.04</v>
+        <v>1.08</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9831,13 +9831,13 @@
         <v>3.2</v>
       </c>
       <c r="M73" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O73" t="n">
-        <v>3.78</v>
+        <v>3.63</v>
       </c>
       <c r="P73" t="n">
         <v>2.44</v>
@@ -9852,10 +9852,10 @@
         <v>4.1</v>
       </c>
       <c r="T73" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="U73" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V73" t="n">
         <v>1.01</v>
@@ -9876,7 +9876,7 @@
         <v>2</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC73" t="n">
         <v>1.38</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AH73" t="n">
         <v>1.31</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="M76" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T76" t="n">
         <v>3.1</v>
       </c>
-      <c r="N76" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O76" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T76" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U76" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V76" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W76" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X76" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AA76" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45929.8125</v>
+        <v>45929.79166666666</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="M77" t="n">
-        <v>3.37</v>
+        <v>2.9</v>
       </c>
       <c r="N77" t="n">
-        <v>5.4</v>
+        <v>3.54</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45929.83333333334</v>
+        <v>45929.8125</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,61 +10473,61 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M78" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N78" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>6</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA78" t="n">
         <v>4.75</v>
       </c>
-      <c r="O78" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P78" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X78" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB78" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH78" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45929.875</v>
+        <v>45929.83333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,126 +10561,384 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M79" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X79" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>45929.875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>45929.89583333334</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M79" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" s="3" t="n">
+      <c r="L81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X81" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3" t="n">
         <v>45929.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>4.38</v>
       </c>
       <c r="N10" t="n">
-        <v>1.54</v>
+        <v>6.62</v>
       </c>
       <c r="O10" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.47</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
-        <v>4.82</v>
+        <v>6.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="T11" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.05</v>
+        <v>4.63</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.55</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>4.44</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>6.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>4.32</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
         <v>3.7</v>
@@ -2373,34 +2373,34 @@
         <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>2.24</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2478,58 +2478,58 @@
         <v>7.5</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
-        <v>7.65</v>
+        <v>8.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.06</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.27</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,31 +2733,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
         <v>1.36</v>
@@ -2766,28 +2766,28 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
         <v>1.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
         <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.21</v>
+        <v>3.32</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>2.66</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="X27" t="n">
-        <v>3.44</v>
+        <v>2.54</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.31</v>
+        <v>2.86</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="T28" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>6.33</v>
+        <v>3.28</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.98</v>
+        <v>2.06</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.55</v>
       </c>
-      <c r="M29" t="n">
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.57</v>
+        <v>2.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.2</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.45</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="AA30" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.36</v>
       </c>
-      <c r="X30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.67</v>
+        <v>4.76</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>3.74</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="X31" t="n">
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>5.95</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>3.66</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.15</v>
+        <v>3.32</v>
       </c>
       <c r="U32" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>4.18</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>4.15</v>
+        <v>3.97</v>
       </c>
       <c r="N33" t="n">
-        <v>5.79</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U33" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>4.83</v>
+        <v>4.99</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
         <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>7.8</v>
+        <v>5.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="R34" t="n">
         <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.3</v>
       </c>
-      <c r="O36" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.76</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="X36" t="n">
-        <v>3.28</v>
+        <v>4.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>3.36</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.92</v>
+        <v>3.8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.25</v>
+        <v>2.52</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
         <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="M39" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="O39" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
         <v>3.3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.66</v>
+        <v>3.85</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>1.77</v>
       </c>
       <c r="O41" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="P41" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.35</v>
+        <v>2.67</v>
       </c>
       <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
-        <v>2.58</v>
+        <v>5.18</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>2.09</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T42" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z42" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC42" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.81</v>
+        <v>1.15</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="O43" t="n">
-        <v>5.18</v>
+        <v>7.8</v>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="R43" t="n">
         <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="T43" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>5.5</v>
+        <v>4.79</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.63</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="P44" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="T44" t="n">
-        <v>3.74</v>
+        <v>2.62</v>
       </c>
       <c r="U44" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="P45" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.65</v>
+        <v>4.22</v>
       </c>
       <c r="R45" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="T45" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="X45" t="n">
-        <v>2.7</v>
+        <v>3.64</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.18</v>
+        <v>2.84</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3.71</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="P46" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.35</v>
+        <v>6.25</v>
       </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
         <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2.13</v>
+        <v>3.68</v>
       </c>
       <c r="P47" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.72</v>
+        <v>2.91</v>
       </c>
       <c r="R47" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="T47" t="n">
-        <v>2.17</v>
+        <v>2.76</v>
       </c>
       <c r="U47" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X47" t="n">
-        <v>4.99</v>
+        <v>3.28</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.98</v>
+        <v>3.08</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,31 +6603,31 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.4</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.45</v>
       </c>
       <c r="U48" t="n">
         <v>1.52</v>
@@ -6636,28 +6636,28 @@
         <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA48" t="n">
         <v>2.65</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6861,52 +6861,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="M50" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="O50" t="n">
         <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S50" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="T50" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AB50" t="n">
         <v>1.22</v>
@@ -7119,22 +7119,22 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33</v>
+        <v>4.72</v>
       </c>
       <c r="P52" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="R52" t="n">
         <v>1.28</v>
@@ -7143,37 +7143,37 @@
         <v>3.22</v>
       </c>
       <c r="T52" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U52" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X52" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,77 +7248,77 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="M53" t="n">
-        <v>7.25</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>13.1</v>
+        <v>2.67</v>
       </c>
       <c r="O53" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.51</v>
-      </c>
-      <c r="P53" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X53" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>4.85</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y54" t="n">
         <v>1.63</v>
       </c>
-      <c r="M54" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N54" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X54" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z54" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AC54" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,77 +7506,77 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>4.42</v>
       </c>
       <c r="O55" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X55" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH55" t="n">
         <v>2.26</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.47</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="M57" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P57" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="Q57" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S57" t="n">
         <v>3.3</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB57" t="n">
         <v>1.44</v>
       </c>
-      <c r="S57" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC57" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>4.42</v>
       </c>
       <c r="O58" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P58" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.22</v>
+        <v>4.46</v>
       </c>
       <c r="R58" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S58" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="T58" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="U58" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="V58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X58" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,58 +8151,58 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O60" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="P60" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S60" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="T60" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U60" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V60" t="n">
         <v>1.04</v>
       </c>
       <c r="W60" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X60" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD60" t="n">
         <v>1.75</v>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,77 +8280,77 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="N61" t="n">
-        <v>2.77</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.57</v>
+        <v>6.4</v>
       </c>
       <c r="R61" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S61" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="T61" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="U61" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="V61" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB61" t="n">
         <v>1.19</v>
       </c>
-      <c r="X61" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC61" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AD61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH61" t="n">
         <v>2.22</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N62" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="O62" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="P62" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>3.57</v>
       </c>
       <c r="R62" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S62" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="T62" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U62" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="V62" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W62" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X62" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.36</v>
       </c>
-      <c r="X62" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC62" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>1.28</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O63" t="n">
-        <v>2.59</v>
+        <v>3.44</v>
       </c>
       <c r="P63" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.83</v>
+        <v>3.26</v>
       </c>
       <c r="R63" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="S63" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="T63" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="U63" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W63" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="X63" t="n">
-        <v>3.74</v>
+        <v>2.63</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>4.96</v>
       </c>
       <c r="N64" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="O64" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="P64" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.99</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R64" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="T64" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="U64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W64" t="n">
         <v>1.31</v>
       </c>
-      <c r="V64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X64" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="Y64" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH64" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M65" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="R65" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S65" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="T65" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U65" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="V65" t="n">
         <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="X65" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Y65" t="n">
         <v>1.85</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,77 +8925,77 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.43</v>
+        <v>2.09</v>
       </c>
       <c r="M66" t="n">
-        <v>5.2</v>
+        <v>3.51</v>
       </c>
       <c r="N66" t="n">
-        <v>5.2</v>
+        <v>3.27</v>
       </c>
       <c r="O66" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="P66" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="Q66" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S66" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="T66" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U66" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V66" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W66" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X66" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA66" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AB66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC66" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH66" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9063,13 +9063,13 @@
         <v>2.13</v>
       </c>
       <c r="O67" t="n">
-        <v>3.75</v>
+        <v>4.14</v>
       </c>
       <c r="P67" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R67" t="n">
         <v>1.46</v>
@@ -9078,16 +9078,16 @@
         <v>2.45</v>
       </c>
       <c r="T67" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="U67" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V67" t="n">
         <v>1.04</v>
       </c>
       <c r="W67" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X67" t="n">
         <v>2.7</v>
@@ -9102,13 +9102,13 @@
         <v>3.98</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC67" t="n">
         <v>1.92</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>1.35</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.23</v>
+        <v>7.5</v>
       </c>
       <c r="M70" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N70" t="n">
-        <v>9.199999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="O70" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.48</v>
+        <v>1.85</v>
       </c>
       <c r="R70" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="S70" t="n">
-        <v>3.98</v>
+        <v>2.98</v>
       </c>
       <c r="T70" t="n">
-        <v>1.93</v>
+        <v>2.51</v>
       </c>
       <c r="U70" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W70" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X70" t="n">
-        <v>6.55</v>
+        <v>3.64</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="Z70" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.59</v>
+        <v>2.09</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AH70" t="n">
-        <v>3.6</v>
+        <v>1.08</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9582,22 +9582,22 @@
         <v>2.38</v>
       </c>
       <c r="P71" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="R71" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S71" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T71" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U71" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V71" t="n">
         <v>1.06</v>
@@ -9606,7 +9606,7 @@
         <v>1.3</v>
       </c>
       <c r="X71" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="Y71" t="n">
         <v>1.98</v>
@@ -9618,13 +9618,13 @@
         <v>3.45</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC71" t="n">
         <v>1.92</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>1.32</v>
       </c>
       <c r="AH71" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>7.64</v>
+        <v>1.59</v>
       </c>
       <c r="M72" t="n">
-        <v>4.69</v>
+        <v>3.35</v>
       </c>
       <c r="N72" t="n">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="P72" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.89</v>
+        <v>5.55</v>
       </c>
       <c r="R72" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S72" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="T72" t="n">
-        <v>2.51</v>
+        <v>3.26</v>
       </c>
       <c r="U72" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V72" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X72" t="n">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.78</v>
+        <v>3.39</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AC72" t="n">
         <v>2</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.08</v>
+        <v>2.18</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9828,19 +9828,19 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="O73" t="n">
         <v>3.63</v>
       </c>
       <c r="P73" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q73" t="n">
         <v>2.38</v>
@@ -9852,10 +9852,10 @@
         <v>4.1</v>
       </c>
       <c r="T73" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="U73" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V73" t="n">
         <v>1.01</v>
@@ -9864,19 +9864,19 @@
         <v>1.07</v>
       </c>
       <c r="X73" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AA73" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC73" t="n">
         <v>1.38</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AH73" t="n">
         <v>1.31</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,61 +10086,61 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10344,22 +10344,22 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M77" t="n">
         <v>2.9</v>
       </c>
       <c r="N77" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="O77" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="P77" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="R77" t="n">
         <v>1.56</v>
@@ -10368,37 +10368,37 @@
         <v>2.34</v>
       </c>
       <c r="T77" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U77" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V77" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z77" t="n">
         <v>1.48</v>
-      </c>
-      <c r="X77" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>1.53</v>
       </c>
       <c r="AA77" t="n">
         <v>5.13</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>1.37</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10860,58 +10860,58 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="M81" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N81" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="O81" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P81" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q81" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T81" t="n">
         <v>3.4</v>
       </c>
-      <c r="R81" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.34</v>
-      </c>
       <c r="U81" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V81" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X81" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA81" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AB81" t="n">
         <v>1.14</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD81" t="n">
         <v>1.75</v>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>

--- a/jogos_2025-09-29.xlsx
+++ b/jogos_2025-09-29.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="M3" t="n">
         <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
         <v>4.85</v>
@@ -831,10 +831,10 @@
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
         <v>2.33</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
         <v>3.7</v>
@@ -957,7 +957,7 @@
         <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
         <v>1.41</v>
@@ -966,13 +966,13 @@
         <v>2.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="AB4" t="n">
         <v>1.14</v>
@@ -997,7 +997,7 @@
         <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
         <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.59</v>
+        <v>7.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
         <v>1.38</v>
@@ -1605,16 +1605,16 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AA9" t="n">
         <v>3.1</v>
@@ -1626,7 +1626,7 @@
         <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>4.38</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>6.62</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>3.47</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>6.49</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.63</v>
+        <v>5.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.38</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>6.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>4.44</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>4.82</v>
+        <v>6.49</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q16" t="n">
         <v>7.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.56</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.94</v>
+        <v>2.57</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.55</v>
+        <v>4.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
         <v>2.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>1.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>10.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.96</v>
+        <v>1.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.51</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>4.65</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>6.61</v>
       </c>
       <c r="O21" t="n">
         <v>2.06</v>
@@ -3135,7 +3135,7 @@
         <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.8</v>
+        <v>6.85</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
@@ -3144,7 +3144,7 @@
         <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
@@ -3159,10 +3159,10 @@
         <v>2.84</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA21" t="n">
         <v>3.9</v>
@@ -3190,7 +3190,7 @@
         <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>6.25</v>
+        <v>2.54</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.41</v>
+        <v>2.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.51</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.86</v>
+        <v>3.31</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.68</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>3.28</v>
+        <v>6.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.06</v>
+        <v>2.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="N29" t="n">
-        <v>3.41</v>
+        <v>2.27</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>3.94</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.36</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
